--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487863_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487863_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.951000000000001</v>
+        <v>8.5138</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4353</v>
+        <v>6.7615</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5157</v>
+        <v>1.7523</v>
       </c>
       <c r="G2" t="n">
         <v>6.5588</v>
@@ -610,13 +610,13 @@
         <v>3.538</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0241</v>
+        <v>-0.4612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7614</v>
+        <v>-0.4352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7373</v>
+        <v>-0.026</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2131</v>
+        <v>2.3454</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4053</v>
+        <v>2.244</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1922</v>
+        <v>0.1014</v>
       </c>
       <c r="G3" t="n">
         <v>5.564</v>
@@ -688,13 +688,13 @@
         <v>3.3299</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.693</v>
+        <v>-0.5608</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2801</v>
+        <v>-0.4414</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4129</v>
+        <v>-0.1193</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5767</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0493</v>
+        <v>1.4463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4026</v>
+        <v>0.6821</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.7641</v>
       </c>
       <c r="G4" t="n">
         <v>0.5038</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0028</v>
+        <v>-0.6058</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6524</v>
+        <v>-0.3729</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3503</v>
+        <v>-0.2329</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1168</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0548</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1039</v>
+        <v>0.0547</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0491</v>
+        <v>0.5165</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0295</v>
+        <v>-2.0831</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8933</v>
+        <v>-0.2878</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9228</v>
+        <v>-1.7953</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3637</v>
+        <v>0.4929</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3875</v>
+        <v>0.0104</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.7512</v>
+        <v>0.4825</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6658</v>
+        <v>-2.576</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4942</v>
+        <v>-0.2982</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1716</v>
+        <v>-2.2778</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9137</v>
+        <v>3.3299</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R5" t="n">
-        <v>4.1624</v>
+        <v>3.538</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.9056</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2428</v>
+        <v>-0.46</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2343</v>
+        <v>-0.4456</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9305</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7513</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4773</v>
+        <v>-0.4215</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.2064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2229</v>
+        <v>-0.2151</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0831</v>
+        <v>-2.0295</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2878</v>
+        <v>0.8933</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7953</v>
+        <v>-2.9228</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4929</v>
+        <v>-0.3637</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0104</v>
+        <v>1.3875</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4825</v>
+        <v>-1.7512</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.576</v>
+        <v>-1.6658</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2982</v>
+        <v>-0.4942</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2778</v>
+        <v>-1.1716</v>
       </c>
       <c r="P6" t="n">
-        <v>3.3299</v>
+        <v>2.9137</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
-        <v>3.538</v>
+        <v>4.1624</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.954</v>
+        <v>-0.3751</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2148</v>
+        <v>-0.3452</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7392</v>
+        <v>-0.0299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>-0.9305</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0175</v>
+        <v>-2.8454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2347</v>
+        <v>-0.6226</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2522</v>
+        <v>-2.2228</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3584</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8364</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9192</v>
+        <v>0.0619</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0828</v>
+        <v>-0.0535</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7442</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4172</v>
+        <v>-3.8669</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5429</v>
+        <v>-2.1981</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8744</v>
+        <v>-1.6689</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4782</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.944</v>
+        <v>-0.3937</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6524</v>
+        <v>-0.3076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0356</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0872</v>
+        <v>-4.9524</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5203</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5202</v>
+        <v>-4.4321</v>
       </c>
       <c r="G10" t="n">
         <v>0.1104</v>
@@ -1234,13 +1234,13 @@
         <v>2.2893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7366</v>
+        <v>-0.6018</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1866</v>
+        <v>-0.14</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4619</v>
       </c>
       <c r="V10" t="n">
         <v>-5.5016</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.565999999999999</v>
+        <v>0.06500000000000039</v>
       </c>
       <c r="E11" t="n">
-        <v>4.622400000000001</v>
+        <v>6.2533</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.1884</v>
+        <v>-6.188400000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>4.205299999999999</v>
+        <v>4.2053</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4298</v>
+        <v>2.429800000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.775700000000001</v>
+        <v>1.7757</v>
       </c>
       <c r="J11" t="n">
         <v>15.7387</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9009</v>
+        <v>4.900900000000001</v>
       </c>
       <c r="L11" t="n">
         <v>10.8379</v>
@@ -1300,7 +1300,7 @@
         <v>-2.4711</v>
       </c>
       <c r="O11" t="n">
-        <v>-9.062200000000001</v>
+        <v>-9.062199999999999</v>
       </c>
       <c r="P11" t="n">
         <v>10.4059</v>
@@ -1312,13 +1312,13 @@
         <v>20.8118</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.669499999999999</v>
+        <v>-4.0384</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.0713</v>
+        <v>-2.4404</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.598</v>
+        <v>-1.5981</v>
       </c>
       <c r="V11" t="n">
         <v>-10.5079</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8373</v>
+        <v>2.7863</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8837</v>
+        <v>3.3964</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0464</v>
+        <v>-0.6101</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3222</v>
+        <v>0.9628</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0469</v>
+        <v>-1.4604</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3691</v>
+        <v>2.4231</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7599</v>
+        <v>2.3182</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7779</v>
+        <v>-1.0642</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.018</v>
+        <v>3.3824</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0821</v>
+        <v>-1.3555</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.731</v>
+        <v>-0.3962</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3512</v>
+        <v>-0.9593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5757</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8293</v>
+        <v>0.2405</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7464</v>
+        <v>0.6642</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1675</v>
+        <v>1.7513</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3351</v>
+        <v>2.9188</v>
       </c>
       <c r="X12" t="n">
         <v>-1.1675</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4609</v>
+        <v>2.3162</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5036</v>
+        <v>1.5834</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0427</v>
+        <v>0.7328</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9628</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4604</v>
+        <v>-0.4966</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4231</v>
+        <v>1.4083</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3182</v>
+        <v>2.0019</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0642</v>
+        <v>-0.2922</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3824</v>
+        <v>2.2941</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3555</v>
+        <v>-1.0901</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3962</v>
+        <v>-0.2043</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9593</v>
+        <v>-0.8858</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8325</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5793</v>
+        <v>0.4637</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3477</v>
+        <v>-0.3186</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2317</v>
+        <v>0.7823</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7513</v>
+        <v>1.9813</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9188</v>
+        <v>1.9813</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1604</v>
+        <v>2.154</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2905</v>
+        <v>2.969</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1301</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>2.6224</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6597</v>
+        <v>1.6534</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8663</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7934</v>
+        <v>1.1085</v>
       </c>
       <c r="V14" t="n">
         <v>0.5838</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8225</v>
+        <v>1.8396</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2619</v>
+        <v>2.9193</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5605</v>
+        <v>-1.0797</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9118000000000001</v>
+        <v>-1.3222</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4966</v>
+        <v>0.0469</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4083</v>
+        <v>-1.3691</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0019</v>
+        <v>0.7599</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2922</v>
+        <v>0.7779</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2941</v>
+        <v>-0.018</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0901</v>
+        <v>-2.0821</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2043</v>
+        <v>-0.731</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8858</v>
+        <v>-1.3512</v>
       </c>
       <c r="P15" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.03</v>
+        <v>1.578</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.64</v>
+        <v>0.8649</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6101</v>
+        <v>0.7131</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9813</v>
+        <v>1.1675</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9813</v>
+        <v>2.3351</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5084</v>
+        <v>0.7903</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4619</v>
+        <v>-1.0333</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9704</v>
+        <v>1.8236</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5367</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9212</v>
+        <v>1.2031</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4308</v>
+        <v>1.284</v>
       </c>
       <c r="V16" t="n">
         <v>0.7076</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2597</v>
+        <v>0.6501</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5769</v>
+        <v>-1.3626</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8365</v>
+        <v>2.0127</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2477</v>
@@ -1780,13 +1780,13 @@
         <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2459</v>
+        <v>0.1445</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1455</v>
+        <v>0.3217</v>
       </c>
       <c r="V17" t="n">
         <v>3.0427</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1333</v>
+        <v>0.429</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5312</v>
+        <v>1.9978</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3978</v>
+        <v>-1.5687</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6988</v>
+        <v>0.3715</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5715</v>
+        <v>0.3902</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2703</v>
+        <v>-0.0188</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9382</v>
+        <v>3.0741</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8207</v>
+        <v>1.7417</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1176</v>
+        <v>1.3324</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6371</v>
+        <v>-2.7026</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2492</v>
+        <v>-1.3515</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3879</v>
+        <v>-1.3512</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8111</v>
+        <v>-0.1724</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6087</v>
+        <v>-0.2657</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2025</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0437</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0437</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2702</v>
+        <v>-0.6848</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6763</v>
+        <v>-0.6383</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9465</v>
+        <v>-0.0465</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3715</v>
+        <v>-0.6988</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3902</v>
+        <v>0.5715</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0188</v>
+        <v>-1.2703</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0741</v>
+        <v>0.9382</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7417</v>
+        <v>0.8207</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3324</v>
+        <v>0.1176</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7026</v>
+        <v>-1.6371</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3515</v>
+        <v>-0.2492</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3512</v>
+        <v>-1.3879</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8716</v>
+        <v>1.2596</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2844</v>
+        <v>0.7581</v>
       </c>
       <c r="V19" t="n">
-        <v>0.23</v>
+        <v>1.0437</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>1.0437</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3145</v>
+        <v>-2.9891</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6319</v>
+        <v>-0.7391</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6825</v>
+        <v>-2.25</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6417</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.216</v>
+        <v>0.1094</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4005</v>
+        <v>0.2934</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6165</v>
+        <v>-0.184</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7651</v>
+        <v>-4.2968</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2257</v>
+        <v>-2.9042</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5394</v>
+        <v>-1.3926</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6266</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5141</v>
+        <v>-0.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3262</v>
+        <v>-0.0047</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1879</v>
+        <v>-0.0411</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.566099999999998</v>
+        <v>2.994799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>6.1884</v>
+        <v>6.188399999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.622400000000001</v>
+        <v>-3.193499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2052</v>
@@ -2170,13 +2170,13 @@
         <v>10.4059</v>
       </c>
       <c r="S22" t="n">
-        <v>5.6694</v>
+        <v>7.0982</v>
       </c>
       <c r="T22" t="n">
-        <v>1.598</v>
+        <v>1.5982</v>
       </c>
       <c r="U22" t="n">
-        <v>4.071599999999999</v>
+        <v>5.5001</v>
       </c>
       <c r="V22" t="n">
         <v>10.5079</v>
